--- a/data/availability/projects/ora/silversands.xlsx
+++ b/data/availability/projects/ora/silversands.xlsx
@@ -461,12 +461,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Silversands latest availability</t>
+          <t>Updated inventory for silversands</t>
         </is>
       </c>
     </row>
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L19"/>
+  <dimension ref="A1:L18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -554,7 +554,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Chalet</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -570,14 +570,14 @@
         <v>151</v>
       </c>
       <c r="G2" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="H2" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Fully Finished</t>
+          <t>Finished</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -587,7 +587,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>North Coast Delivery</t>
+          <t>2028</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -627,7 +627,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Fully Finished</t>
+          <t>Finished</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -637,7 +637,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>North Coast Delivery</t>
+          <t>2028</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -677,7 +677,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Fully Finished</t>
+          <t>Finished</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -687,7 +687,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>North Coast Delivery</t>
+          <t>2028</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Fully Finished</t>
+          <t>Finished</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -737,7 +737,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>North Coast Delivery</t>
+          <t>2028</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -758,26 +758,26 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E6" t="n">
         <v>202</v>
       </c>
       <c r="F6" t="n">
-        <v>202</v>
+        <v>307</v>
       </c>
       <c r="G6" t="n">
         <v>47</v>
       </c>
       <c r="H6" t="n">
-        <v>47</v>
+        <v>76</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Fully Finished</t>
+          <t>Finished</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>North Coast Delivery</t>
+          <t>2028</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -804,7 +804,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Twin House</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -814,20 +814,20 @@
         <v>1</v>
       </c>
       <c r="E7" t="n">
-        <v>307</v>
+        <v>232</v>
       </c>
       <c r="F7" t="n">
-        <v>307</v>
+        <v>232</v>
       </c>
       <c r="G7" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H7" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Fully Finished</t>
+          <t>Finished</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -837,7 +837,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>North Coast Delivery</t>
+          <t>2028</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -858,26 +858,26 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D8" t="n">
         <v>2</v>
       </c>
       <c r="E8" t="n">
-        <v>232</v>
+        <v>345</v>
       </c>
       <c r="F8" t="n">
-        <v>345</v>
+        <v>380</v>
       </c>
       <c r="G8" t="n">
-        <v>75</v>
+        <v>128</v>
       </c>
       <c r="H8" t="n">
-        <v>128</v>
+        <v>180</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Fully Finished</t>
+          <t>Finished</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -887,7 +887,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>North Coast Delivery</t>
+          <t>2028</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -904,45 +904,45 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Standalone Villa</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D9" t="n">
         <v>1</v>
       </c>
       <c r="E9" t="n">
-        <v>380</v>
+        <v>127</v>
       </c>
       <c r="F9" t="n">
-        <v>380</v>
+        <v>127</v>
       </c>
       <c r="G9" t="n">
-        <v>180</v>
+        <v>21</v>
       </c>
       <c r="H9" t="n">
-        <v>180</v>
+        <v>21</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Fully Finished</t>
+          <t>Finished</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Crystalline</t>
+          <t>Silvertown</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>North Coast Delivery</t>
+          <t>2028</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>5% + 5% + 5%, installments over 8 years</t>
+          <t>5% + 5%, installments over 10 years</t>
         </is>
       </c>
     </row>
@@ -954,30 +954,30 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Chalet</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C10" t="n">
+        <v>3</v>
+      </c>
+      <c r="D10" t="n">
         <v>2</v>
       </c>
-      <c r="D10" t="n">
-        <v>1</v>
-      </c>
       <c r="E10" t="n">
-        <v>127</v>
+        <v>156</v>
       </c>
       <c r="F10" t="n">
-        <v>127</v>
+        <v>186</v>
       </c>
       <c r="G10" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="H10" t="n">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Fully Finished</t>
+          <t>Finished</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -987,7 +987,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Lagoon View</t>
+          <t>2028</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1004,30 +1004,30 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Chalet</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E11" t="n">
-        <v>156</v>
+        <v>192</v>
       </c>
       <c r="F11" t="n">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="G11" t="n">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="H11" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Fully Finished</t>
+          <t>Finished</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1037,7 +1037,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Lagoon View</t>
+          <t>2028</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1054,30 +1054,30 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Chalet</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E12" t="n">
-        <v>192</v>
+        <v>150</v>
       </c>
       <c r="F12" t="n">
-        <v>192</v>
+        <v>170</v>
       </c>
       <c r="G12" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="H12" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Fully Finished</t>
+          <t>Finished</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1087,7 +1087,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Lagoon View</t>
+          <t>2028</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1104,30 +1104,30 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E13" t="n">
-        <v>150</v>
+        <v>263</v>
       </c>
       <c r="F13" t="n">
-        <v>170</v>
+        <v>263</v>
       </c>
       <c r="G13" t="n">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="H13" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Fully Finished</t>
+          <t>Finished</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1137,7 +1137,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Lagoon View</t>
+          <t>2028</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1154,30 +1154,30 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>4</v>
       </c>
       <c r="D14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E14" t="n">
-        <v>263</v>
+        <v>190</v>
       </c>
       <c r="F14" t="n">
-        <v>263</v>
+        <v>210</v>
       </c>
       <c r="G14" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="H14" t="n">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Fully Finished</t>
+          <t>Finished</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Lagoon View</t>
+          <t>2028</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1208,26 +1208,26 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D15" t="n">
         <v>1</v>
       </c>
       <c r="E15" t="n">
-        <v>190</v>
+        <v>250</v>
       </c>
       <c r="F15" t="n">
-        <v>190</v>
+        <v>250</v>
       </c>
       <c r="G15" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="H15" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Fully Finished</t>
+          <t>Finished</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Lagoon View</t>
+          <t>2028</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1254,45 +1254,45 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Standalone Villa</t>
+          <t>Penthouse</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E16" t="n">
-        <v>210</v>
+        <v>96</v>
       </c>
       <c r="F16" t="n">
-        <v>250</v>
+        <v>96</v>
       </c>
       <c r="G16" t="n">
-        <v>68</v>
+        <v>21</v>
       </c>
       <c r="H16" t="n">
-        <v>75</v>
+        <v>21</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Fully Finished</t>
+          <t>Finished</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Silvertown</t>
+          <t>The Cove</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Lagoon View</t>
+          <t>2028</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>5% + 5%, installments over 10 years</t>
+          <t>5% + 5%, equal installments over 8 years</t>
         </is>
       </c>
     </row>
@@ -1304,30 +1304,30 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Penthouse</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D17" t="n">
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>96</v>
+        <v>123</v>
       </c>
       <c r="F17" t="n">
-        <v>96</v>
+        <v>123</v>
       </c>
       <c r="G17" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H17" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Fully Finished</t>
+          <t>Finished</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>30 equal installments</t>
+          <t>2028</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -1358,91 +1358,41 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D18" t="n">
         <v>1</v>
       </c>
       <c r="E18" t="n">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="F18" t="n">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="G18" t="n">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="H18" t="n">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Fully Finished</t>
+          <t>Finished</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>The Cove</t>
+          <t>Branded Residence</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>30 equal installments</t>
+          <t>2028</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>5% + 5%, equal installments over 8 years</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>silversands</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Apartment</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>2</v>
-      </c>
-      <c r="D19" t="n">
-        <v>1</v>
-      </c>
-      <c r="E19" t="n">
-        <v>130</v>
-      </c>
-      <c r="F19" t="n">
-        <v>130</v>
-      </c>
-      <c r="G19" t="n">
-        <v>38</v>
-      </c>
-      <c r="H19" t="n">
-        <v>38</v>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>Fully Finished &amp; Serviced</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>Branded Residence</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>Silversands Caribbean Branded</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>5% + 5% + 5%, installments over 6 years</t>
+          <t>5% + 5% + 5% – 6 years</t>
         </is>
       </c>
     </row>
@@ -1535,12 +1485,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Chalet</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>SS-CRY-2BR</t>
+          <t>SS-CR-2BR</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -1553,7 +1503,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fully Finished</t>
+          <t>Finished</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -1561,20 +1511,20 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>148-154 sqm</t>
+          <t>148-154 SQM</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Landscape / City</t>
+          <t>Landscape</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>25000000</v>
+        <v>29000000</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>North Coast Delivery</t>
+          <t>2028</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -1601,7 +1551,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>SS-CRY-2BR-DUP</t>
+          <t>SS-CR-2BR-DUP</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -1614,7 +1564,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fully Finished</t>
+          <t>Finished</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1622,12 +1572,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>160 sqm</t>
+          <t>160 SQM Duplex</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Landscape / City</t>
+          <t>Landscape</t>
         </is>
       </c>
       <c r="J3" t="n">
@@ -1635,7 +1585,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>North Coast Delivery</t>
+          <t>2028</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -1662,7 +1612,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>SS-CRY-3BR-DUP</t>
+          <t>SS-CR-3BR-DUP</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1675,7 +1625,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fully Finished</t>
+          <t>Finished</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1683,12 +1633,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>180 sqm</t>
+          <t>180 SQM Duplex</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Landscape / City</t>
+          <t>Landscape</t>
         </is>
       </c>
       <c r="J4" t="n">
@@ -1696,7 +1646,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>North Coast Delivery</t>
+          <t>2028</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -1723,7 +1673,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>SS-CRY-UP-CHALET</t>
+          <t>SS-CR-UP-CHALET</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1736,7 +1686,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fully Finished</t>
+          <t>Finished</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1744,12 +1694,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Upper Chalet 237 sqm</t>
+          <t>Upper Chalet 237 SQM</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Landscape / City</t>
+          <t>Landscape</t>
         </is>
       </c>
       <c r="J5" t="n">
@@ -1757,7 +1707,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>North Coast Delivery</t>
+          <t>2028</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1784,7 +1734,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>SS-CRY-G-CHALET</t>
+          <t>SS-CR-G-CHALET</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1797,7 +1747,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fully Finished</t>
+          <t>Finished</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1805,12 +1755,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Ground Chalet 204 sqm</t>
+          <t>Ground Chalet 204 SQM</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Landscape / City</t>
+          <t>Landscape</t>
         </is>
       </c>
       <c r="J6" t="n">
@@ -1818,7 +1768,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>North Coast Delivery</t>
+          <t>2028</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1845,7 +1795,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>SS-CRY-TWH</t>
+          <t>SS-CR-TWH</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1854,11 +1804,11 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fully Finished</t>
+          <t>Finished</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1866,12 +1816,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Twin House 202 sqm</t>
+          <t>Twin House 202 SQM</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Landscape / City</t>
+          <t>Landscape</t>
         </is>
       </c>
       <c r="J7" t="n">
@@ -1879,7 +1829,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>North Coast Delivery</t>
+          <t>2028</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1906,7 +1856,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>SS-CRY-TWHL</t>
+          <t>SS-CR-TWH-L</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1919,7 +1869,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fully Finished</t>
+          <t>Finished</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1927,12 +1877,12 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Twin House L 307 sqm</t>
+          <t>Twin House L 307 SQM</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Landscape / City</t>
+          <t>Landscape</t>
         </is>
       </c>
       <c r="J8" t="n">
@@ -1940,7 +1890,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>North Coast Delivery</t>
+          <t>2028</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1967,7 +1917,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>SS-CRY-V4A</t>
+          <t>SS-CR-V4A</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1980,7 +1930,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Fully Finished</t>
+          <t>Finished</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1988,12 +1938,12 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Villa 4A 232 sqm</t>
+          <t>Villa 4A 232 SQM</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Landscape / City</t>
+          <t>Landscape</t>
         </is>
       </c>
       <c r="J9" t="n">
@@ -2001,7 +1951,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>North Coast Delivery</t>
+          <t>2028</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -2028,7 +1978,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>SS-CRY-V3B</t>
+          <t>SS-CR-V3B</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2037,11 +1987,11 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Fully Finished</t>
+          <t>Finished</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2049,12 +1999,12 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Villa 3B 345 sqm</t>
+          <t>Villa 3B 345 SQM</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Landscape / City</t>
+          <t>Landscape</t>
         </is>
       </c>
       <c r="J10" t="n">
@@ -2062,7 +2012,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>North Coast Delivery</t>
+          <t>2028</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -2089,7 +2039,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>SS-CRY-V2A</t>
+          <t>SS-CR-V2A</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2102,7 +2052,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Fully Finished</t>
+          <t>Finished</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2110,12 +2060,12 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Villa 2A 380 sqm</t>
+          <t>Villa 2A 380 SQM</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Landscape / City</t>
+          <t>Landscape</t>
         </is>
       </c>
       <c r="J11" t="n">
@@ -2123,7 +2073,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>North Coast Delivery</t>
+          <t>2028</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -2145,7 +2095,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Chalet</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -2163,7 +2113,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Fully Finished</t>
+          <t>Finished</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2171,12 +2121,12 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>127 sqm</t>
+          <t>127 SQM</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Landscape / City</t>
+          <t>Landscape</t>
         </is>
       </c>
       <c r="J12" t="n">
@@ -2184,7 +2134,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Lagoon View</t>
+          <t>2028</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -2206,7 +2156,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Chalet</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2224,7 +2174,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Fully Finished</t>
+          <t>Finished</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2232,12 +2182,12 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>156 sqm</t>
+          <t>156 SQM</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Landscape / City</t>
+          <t>Landscape</t>
         </is>
       </c>
       <c r="J13" t="n">
@@ -2245,7 +2195,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Lagoon View</t>
+          <t>2028</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -2267,7 +2217,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Chalet</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2285,7 +2235,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Fully Finished</t>
+          <t>Finished</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2293,12 +2243,12 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>186 sqm</t>
+          <t>186 SQM</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Landscape / City</t>
+          <t>Landscape</t>
         </is>
       </c>
       <c r="J14" t="n">
@@ -2306,7 +2256,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Lagoon View</t>
+          <t>2028</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -2328,7 +2278,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Chalet</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2346,7 +2296,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Fully Finished</t>
+          <t>Finished</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2354,12 +2304,12 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>192 sqm</t>
+          <t>192 SQM</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Landscape / City</t>
+          <t>Landscape</t>
         </is>
       </c>
       <c r="J15" t="n">
@@ -2367,7 +2317,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Lagoon View</t>
+          <t>2028</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -2389,7 +2339,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2407,7 +2357,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Fully Finished</t>
+          <t>Finished</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2415,12 +2365,12 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Townhouse S 150 sqm</t>
+          <t>Townhouse S 150 SQM</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Landscape / City</t>
+          <t>Landscape</t>
         </is>
       </c>
       <c r="J16" t="n">
@@ -2428,7 +2378,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Lagoon View</t>
+          <t>2028</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -2450,7 +2400,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2468,7 +2418,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Fully Finished</t>
+          <t>Finished</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2476,12 +2426,12 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Townhouse M 170 sqm</t>
+          <t>Townhouse M 170 SQM</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Landscape / City</t>
+          <t>Landscape</t>
         </is>
       </c>
       <c r="J17" t="n">
@@ -2489,7 +2439,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Lagoon View</t>
+          <t>2028</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -2511,7 +2461,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2529,7 +2479,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Fully Finished</t>
+          <t>Finished</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2537,12 +2487,12 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Townhouse L 263 sqm</t>
+          <t>Townhouse L 263 SQM</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Landscape / City</t>
+          <t>Landscape</t>
         </is>
       </c>
       <c r="J18" t="n">
@@ -2550,7 +2500,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Lagoon View</t>
+          <t>2028</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -2586,11 +2536,11 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Fully Finished</t>
+          <t>Finished</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2598,12 +2548,12 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Villa S 190 sqm</t>
+          <t>Villa S 190 SQM</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Landscape / City</t>
+          <t>Landscape</t>
         </is>
       </c>
       <c r="J19" t="n">
@@ -2611,7 +2561,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Lagoon View</t>
+          <t>2028</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -2651,7 +2601,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Fully Finished</t>
+          <t>Finished</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2659,12 +2609,12 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Villa M 210 sqm</t>
+          <t>Villa M 210 SQM</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Landscape / City</t>
+          <t>Landscape</t>
         </is>
       </c>
       <c r="J20" t="n">
@@ -2672,7 +2622,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Lagoon View</t>
+          <t>2028</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -2708,11 +2658,11 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Fully Finished</t>
+          <t>Finished</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2720,12 +2670,12 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Villa L 250 sqm</t>
+          <t>Villa L 250 SQM</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Landscape / City</t>
+          <t>Landscape</t>
         </is>
       </c>
       <c r="J21" t="n">
@@ -2733,7 +2683,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Lagoon View</t>
+          <t>2028</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -2760,7 +2710,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>SS-COVE-2BR-PENT</t>
+          <t>SS-CV-2BR-PH</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -2773,7 +2723,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Fully Finished</t>
+          <t>Finished</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -2781,12 +2731,12 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>96 sqm + Roof 76 sqm</t>
+          <t>96 + 76 SQM Roof</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Landscape / City</t>
+          <t>Landscape</t>
         </is>
       </c>
       <c r="J22" t="n">
@@ -2794,7 +2744,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>30 equal installments</t>
+          <t>2028</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -2821,7 +2771,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>SS-COVE-3BR-TYP</t>
+          <t>SS-CV-3BR</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -2834,7 +2784,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Fully Finished</t>
+          <t>Finished</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -2842,12 +2792,12 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>123 sqm</t>
+          <t>123 SQM Typical</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Landscape / City</t>
+          <t>Landscape</t>
         </is>
       </c>
       <c r="J23" t="n">
@@ -2855,7 +2805,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>30 equal installments</t>
+          <t>2028</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -2882,7 +2832,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>SS-BRANDED-2BR</t>
+          <t>SS-BR-2BR</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -2895,7 +2845,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Fully Finished &amp; Serviced</t>
+          <t>Finished</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -2903,12 +2853,12 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>125/135 sqm</t>
+          <t>125/135 SQM Branded Apartment</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Landscape / City</t>
+          <t>Landscape</t>
         </is>
       </c>
       <c r="J24" t="n">
@@ -2916,12 +2866,12 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Silversands Caribbean Branded</t>
+          <t>2028</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>5% + 5% + 5%, installments over 6 years</t>
+          <t>5% + 5% + 5% – 6 years</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">

--- a/data/availability/projects/ora/silversands.xlsx
+++ b/data/availability/projects/ora/silversands.xlsx
@@ -587,7 +587,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -637,7 +637,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -687,7 +687,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -737,7 +737,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -837,7 +837,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -887,7 +887,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -937,7 +937,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -987,7 +987,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1037,7 +1037,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1087,7 +1087,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1137,7 +1137,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1287,7 +1287,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -1387,7 +1387,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -1585,7 +1585,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -1646,7 +1646,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -1707,7 +1707,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1768,7 +1768,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1829,7 +1829,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -2012,7 +2012,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -2073,7 +2073,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -2134,7 +2134,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -2195,7 +2195,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -2317,7 +2317,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -2378,7 +2378,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -2500,7 +2500,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -2622,7 +2622,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -2683,7 +2683,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -2744,7 +2744,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -2805,7 +2805,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
